--- a/招生信息/2022年录取分.xlsx
+++ b/招生信息/2022年录取分.xlsx
@@ -4,19 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9840"/>
+    <workbookView windowWidth="28260" windowHeight="12840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="103">
   <si>
-    <t xml:space="preserve">浙江树人学院2023年录取情况一览表       
+    <t xml:space="preserve">浙江树人学院2022年录取情况一览表       
 </t>
   </si>
   <si>
@@ -329,7 +342,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -351,34 +364,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -392,14 +377,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -439,6 +416,21 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -489,7 +481,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -504,55 +517,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -570,31 +541,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -618,6 +577,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -630,7 +601,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -654,7 +649,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -673,6 +680,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -714,21 +727,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -757,6 +755,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -815,148 +828,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -979,52 +992,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1296,7 +1309,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="B1:I357"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="3.75" customWidth="1"/>
   </cols>
@@ -1313,7 +1326,7 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="15" spans="2:9">
+    <row r="2" spans="2:9">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1351,7 +1364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:9">
+    <row r="4" ht="17.55" spans="2:9">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -1377,7 +1390,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:9">
+    <row r="5" ht="17.55" spans="2:9">
       <c r="B5" s="3"/>
       <c r="C5" s="3" t="s">
         <v>12</v>
@@ -1401,7 +1414,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:9">
+    <row r="6" ht="17.55" spans="2:9">
       <c r="B6" s="3"/>
       <c r="C6" s="3" t="s">
         <v>13</v>
@@ -1425,7 +1438,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="2:9">
+    <row r="7" ht="17.55" spans="2:9">
       <c r="B7" s="3"/>
       <c r="C7" s="3" t="s">
         <v>14</v>
@@ -1449,7 +1462,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="8" ht="24.75" spans="2:9">
+    <row r="8" ht="28.75" spans="2:9">
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
         <v>15</v>
@@ -1473,7 +1486,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:9">
+    <row r="9" ht="17.55" spans="2:9">
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
         <v>16</v>
@@ -1497,7 +1510,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:9">
+    <row r="10" ht="17.55" spans="2:9">
       <c r="B10" s="3"/>
       <c r="C10" s="3" t="s">
         <v>17</v>
@@ -1521,7 +1534,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:9">
+    <row r="11" ht="17.55" spans="2:9">
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
         <v>18</v>
@@ -1545,7 +1558,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:9">
+    <row r="12" ht="17.55" spans="2:9">
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
         <v>19</v>
@@ -1569,7 +1582,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="13" ht="15" spans="2:9">
+    <row r="13" ht="17.55" spans="2:9">
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
         <v>20</v>
@@ -1593,7 +1606,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="2:9">
+    <row r="14" ht="17.55" spans="2:9">
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
         <v>21</v>
@@ -1617,7 +1630,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="15" ht="15" spans="2:9">
+    <row r="15" ht="17.55" spans="2:9">
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
         <v>22</v>
@@ -1641,7 +1654,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:9">
+    <row r="16" ht="28.75" spans="2:9">
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
         <v>23</v>
@@ -1665,7 +1678,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:9">
+    <row r="17" ht="17.55" spans="2:9">
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
         <v>24</v>
@@ -1689,7 +1702,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:9">
+    <row r="18" ht="17.55" spans="2:9">
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
         <v>25</v>
@@ -1713,7 +1726,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="19" ht="24.75" spans="2:9">
+    <row r="19" ht="28.75" spans="2:9">
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
         <v>26</v>
@@ -1737,7 +1750,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="20" ht="24.75" spans="2:9">
+    <row r="20" ht="28.75" spans="2:9">
       <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
         <v>27</v>
@@ -1761,7 +1774,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="21" ht="24.75" spans="2:9">
+    <row r="21" ht="28.75" spans="2:9">
       <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
         <v>28</v>
@@ -1785,7 +1798,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="22" ht="48.75" spans="2:9">
+    <row r="22" ht="70.75" spans="2:9">
       <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
         <v>29</v>
@@ -1809,7 +1822,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="23" ht="24.75" spans="2:9">
+    <row r="23" ht="28.75" spans="2:9">
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
         <v>30</v>
@@ -1833,7 +1846,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:9">
+    <row r="24" ht="17.55" spans="2:9">
       <c r="B24" s="3"/>
       <c r="C24" s="3" t="s">
         <v>31</v>
@@ -1857,7 +1870,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="25" ht="15" spans="2:9">
+    <row r="25" ht="17.55" spans="2:9">
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
         <v>32</v>
@@ -1881,7 +1894,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:9">
+    <row r="26" ht="17.55" spans="2:9">
       <c r="B26" s="3"/>
       <c r="C26" s="3" t="s">
         <v>33</v>
@@ -1905,7 +1918,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="27" ht="15" spans="2:9">
+    <row r="27" ht="17.55" spans="2:9">
       <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
         <v>34</v>
@@ -1929,7 +1942,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:9">
+    <row r="28" ht="17.55" spans="2:9">
       <c r="B28" s="3"/>
       <c r="C28" s="3" t="s">
         <v>35</v>
@@ -1953,7 +1966,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="29" ht="24.75" spans="2:9">
+    <row r="29" ht="28.75" spans="2:9">
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
         <v>36</v>
@@ -1977,7 +1990,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:9">
+    <row r="30" ht="17.55" spans="2:9">
       <c r="B30" s="3"/>
       <c r="C30" s="3" t="s">
         <v>37</v>
@@ -2001,7 +2014,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="31" ht="15" spans="2:9">
+    <row r="31" ht="17.55" spans="2:9">
       <c r="B31" s="3"/>
       <c r="C31" s="3" t="s">
         <v>38</v>
@@ -2025,7 +2038,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="32" ht="24.75" spans="2:9">
+    <row r="32" ht="28.75" spans="2:9">
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
         <v>39</v>
@@ -2049,7 +2062,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="33" ht="15" spans="2:9">
+    <row r="33" ht="28.75" spans="2:9">
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
         <v>40</v>
@@ -2073,7 +2086,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="34" ht="24.75" spans="2:9">
+    <row r="34" ht="42.75" spans="2:9">
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
         <v>41</v>
@@ -2097,7 +2110,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="35" ht="15" spans="2:9">
+    <row r="35" ht="17.55" spans="2:9">
       <c r="B35" s="3"/>
       <c r="C35" s="3" t="s">
         <v>42</v>
@@ -2121,7 +2134,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="36" ht="24.75" spans="2:9">
+    <row r="36" ht="28.75" spans="2:9">
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
         <v>43</v>
@@ -2145,7 +2158,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="37" ht="15" spans="2:9">
+    <row r="37" ht="17.55" spans="2:9">
       <c r="B37" s="3"/>
       <c r="C37" s="3" t="s">
         <v>44</v>
@@ -2169,7 +2182,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="38" ht="15" spans="2:9">
+    <row r="38" ht="17.55" spans="2:9">
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
         <v>45</v>
@@ -2193,7 +2206,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="39" ht="24.75" spans="2:9">
+    <row r="39" ht="28.75" spans="2:9">
       <c r="B39" s="3"/>
       <c r="C39" s="3" t="s">
         <v>46</v>
@@ -2217,7 +2230,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="40" ht="24.75" spans="2:9">
+    <row r="40" ht="28.75" spans="2:9">
       <c r="B40" s="3"/>
       <c r="C40" s="3" t="s">
         <v>47</v>
@@ -2241,7 +2254,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="41" ht="15" spans="2:9">
+    <row r="41" ht="17.55" spans="2:9">
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
         <v>48</v>
@@ -2265,7 +2278,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="42" ht="15" spans="2:9">
+    <row r="42" ht="17.55" spans="2:9">
       <c r="B42" s="3"/>
       <c r="C42" s="3" t="s">
         <v>49</v>
@@ -2313,7 +2326,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="44" ht="15" spans="2:9">
+    <row r="44" ht="17.55" spans="2:9">
       <c r="B44" s="3" t="s">
         <v>51</v>
       </c>
@@ -2339,7 +2352,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="45" ht="24.75" spans="2:9">
+    <row r="45" ht="28.75" spans="2:9">
       <c r="B45" s="3"/>
       <c r="C45" s="3" t="s">
         <v>53</v>
@@ -2363,7 +2376,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="46" ht="15" spans="2:9">
+    <row r="46" ht="17.55" spans="2:9">
       <c r="B46" s="3"/>
       <c r="C46" s="3" t="s">
         <v>54</v>
@@ -2411,7 +2424,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="48" ht="15" spans="2:9">
+    <row r="48" ht="17.55" spans="2:9">
       <c r="B48" s="3" t="s">
         <v>56</v>
       </c>
@@ -2449,7 +2462,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" ht="24.75" spans="2:9">
+    <row r="50" ht="28.75" spans="2:9">
       <c r="B50" s="3" t="s">
         <v>57</v>
       </c>
@@ -2475,7 +2488,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="51" ht="15" spans="2:9">
+    <row r="51" ht="17.55" spans="2:9">
       <c r="B51" s="3"/>
       <c r="C51" s="3" t="s">
         <v>31</v>
@@ -2499,7 +2512,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="52" ht="15" spans="2:9">
+    <row r="52" ht="17.55" spans="2:9">
       <c r="B52" s="3"/>
       <c r="C52" s="3" t="s">
         <v>12</v>
@@ -2523,7 +2536,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" ht="15" spans="2:9">
+    <row r="53" ht="28.75" spans="2:9">
       <c r="B53" s="3"/>
       <c r="C53" s="3" t="s">
         <v>23</v>
@@ -2571,7 +2584,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="55" ht="24.75" spans="2:9">
+    <row r="55" ht="28.75" spans="2:9">
       <c r="B55" s="3" t="s">
         <v>58</v>
       </c>
@@ -2621,7 +2634,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="57" ht="24.75" spans="2:9">
+    <row r="57" ht="28.75" spans="2:9">
       <c r="B57" s="3" t="s">
         <v>61</v>
       </c>
@@ -2647,7 +2660,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="58" ht="15" spans="2:9">
+    <row r="58" ht="28.75" spans="2:9">
       <c r="B58" s="3"/>
       <c r="C58" s="3" t="s">
         <v>40</v>
@@ -2671,7 +2684,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="59" ht="15" spans="2:9">
+    <row r="59" ht="17.55" spans="2:9">
       <c r="B59" s="3"/>
       <c r="C59" s="3" t="s">
         <v>17</v>
@@ -2695,7 +2708,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="60" ht="15" spans="2:9">
+    <row r="60" ht="17.55" spans="2:9">
       <c r="B60" s="3"/>
       <c r="C60" s="3" t="s">
         <v>16</v>
@@ -2719,7 +2732,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="61" ht="15" spans="2:9">
+    <row r="61" ht="17.55" spans="2:9">
       <c r="B61" s="3"/>
       <c r="C61" s="3" t="s">
         <v>44</v>
@@ -2767,7 +2780,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="63" ht="24.75" spans="2:9">
+    <row r="63" ht="28.75" spans="2:9">
       <c r="B63" s="3" t="s">
         <v>62</v>
       </c>
@@ -2793,7 +2806,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="64" ht="15" spans="2:9">
+    <row r="64" ht="17.55" spans="2:9">
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
         <v>31</v>
@@ -2817,7 +2830,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" ht="15" spans="2:9">
+    <row r="65" ht="17.55" spans="2:9">
       <c r="B65" s="3"/>
       <c r="C65" s="3" t="s">
         <v>13</v>
@@ -2841,7 +2854,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="66" ht="15" spans="2:9">
+    <row r="66" ht="17.55" spans="2:9">
       <c r="B66" s="3"/>
       <c r="C66" s="3" t="s">
         <v>11</v>
@@ -2889,7 +2902,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="68" ht="15" spans="2:9">
+    <row r="68" ht="17.55" spans="2:9">
       <c r="B68" s="3" t="s">
         <v>63</v>
       </c>
@@ -2927,7 +2940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" ht="24.75" spans="2:9">
+    <row r="70" ht="28.75" spans="2:9">
       <c r="B70" s="3" t="s">
         <v>64</v>
       </c>
@@ -2953,7 +2966,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="71" ht="15" spans="2:9">
+    <row r="71" ht="17.55" spans="2:9">
       <c r="B71" s="3"/>
       <c r="C71" s="3" t="s">
         <v>60</v>
@@ -2977,7 +2990,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="72" ht="15" spans="2:9">
+    <row r="72" ht="17.55" spans="2:9">
       <c r="B72" s="3"/>
       <c r="C72" s="3" t="s">
         <v>65</v>
@@ -3001,7 +3014,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="73" ht="15" spans="2:9">
+    <row r="73" ht="17.55" spans="2:9">
       <c r="B73" s="3"/>
       <c r="C73" s="3" t="s">
         <v>66</v>
@@ -3035,7 +3048,7 @@
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" ht="15" spans="2:9">
+    <row r="75" ht="17.55" spans="2:9">
       <c r="B75" s="3" t="s">
         <v>67</v>
       </c>
@@ -3047,7 +3060,7 @@
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
     </row>
-    <row r="76" ht="14.25" spans="2:9">
+    <row r="76" ht="17.55" spans="2:9">
       <c r="B76" s="3" t="s">
         <v>2</v>
       </c>
@@ -3073,7 +3086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" ht="24.75" spans="2:9">
+    <row r="77" ht="28.75" spans="2:9">
       <c r="B77" s="3" t="e">
         <v>#REF!</v>
       </c>
@@ -3125,7 +3138,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="79" ht="15" spans="2:9">
+    <row r="79" spans="2:9">
       <c r="B79" s="3" t="s">
         <v>71</v>
       </c>
@@ -3163,7 +3176,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" ht="24.75" spans="2:9">
+    <row r="81" ht="28.75" spans="2:9">
       <c r="B81" s="3" t="s">
         <v>72</v>
       </c>
@@ -3189,7 +3202,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="82" ht="24.75" spans="2:9">
+    <row r="82" ht="28.75" spans="2:9">
       <c r="B82" s="3"/>
       <c r="C82" s="3" t="s">
         <v>30</v>
@@ -3213,7 +3226,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="83" ht="15" spans="2:9">
+    <row r="83" ht="17.55" spans="2:9">
       <c r="B83" s="3"/>
       <c r="C83" s="3" t="s">
         <v>31</v>
@@ -3237,7 +3250,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="84" ht="15" spans="2:9">
+    <row r="84" ht="17.55" spans="2:9">
       <c r="B84" s="3"/>
       <c r="C84" s="3" t="s">
         <v>32</v>
@@ -3261,7 +3274,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="85" ht="15" spans="2:9">
+    <row r="85" ht="17.55" spans="2:9">
       <c r="B85" s="3"/>
       <c r="C85" s="3" t="s">
         <v>33</v>
@@ -3285,7 +3298,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="86" ht="15" spans="2:9">
+    <row r="86" ht="17.55" spans="2:9">
       <c r="B86" s="3"/>
       <c r="C86" s="3" t="s">
         <v>34</v>
@@ -3309,7 +3322,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="87" ht="15" spans="2:9">
+    <row r="87" ht="17.55" spans="2:9">
       <c r="B87" s="3"/>
       <c r="C87" s="3" t="s">
         <v>19</v>
@@ -3333,7 +3346,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="88" ht="15" spans="2:9">
+    <row r="88" ht="17.55" spans="2:9">
       <c r="B88" s="3"/>
       <c r="C88" s="3" t="s">
         <v>20</v>
@@ -3357,7 +3370,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="89" ht="15" spans="2:9">
+    <row r="89" ht="17.55" spans="2:9">
       <c r="B89" s="3"/>
       <c r="C89" s="3" t="s">
         <v>73</v>
@@ -3381,7 +3394,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="90" ht="15" spans="2:9">
+    <row r="90" ht="28.75" spans="2:9">
       <c r="B90" s="3"/>
       <c r="C90" s="3" t="s">
         <v>23</v>
@@ -3405,7 +3418,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="91" ht="15" spans="2:9">
+    <row r="91" ht="17.55" spans="2:9">
       <c r="B91" s="3"/>
       <c r="C91" s="3" t="s">
         <v>25</v>
@@ -3429,7 +3442,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="92" ht="15" spans="2:9">
+    <row r="92" ht="17.55" spans="2:9">
       <c r="B92" s="3"/>
       <c r="C92" s="3" t="s">
         <v>11</v>
@@ -3453,7 +3466,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="93" ht="15" spans="2:9">
+    <row r="93" ht="17.55" spans="2:9">
       <c r="B93" s="3"/>
       <c r="C93" s="3" t="s">
         <v>12</v>
@@ -3477,7 +3490,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="94" ht="15" spans="2:9">
+    <row r="94" ht="17.55" spans="2:9">
       <c r="B94" s="3"/>
       <c r="C94" s="3" t="s">
         <v>13</v>
@@ -3501,7 +3514,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="95" ht="15" spans="2:9">
+    <row r="95" ht="17.55" spans="2:9">
       <c r="B95" s="3"/>
       <c r="C95" s="3" t="s">
         <v>24</v>
@@ -3525,7 +3538,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="96" ht="24.75" spans="2:9">
+    <row r="96" ht="28.75" spans="2:9">
       <c r="B96" s="3"/>
       <c r="C96" s="3" t="s">
         <v>26</v>
@@ -3573,7 +3586,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="98" ht="15" spans="2:9">
+    <row r="98" ht="17.55" spans="2:9">
       <c r="B98" s="3" t="s">
         <v>74</v>
       </c>
@@ -3599,7 +3612,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="99" ht="15" spans="2:9">
+    <row r="99" ht="17.55" spans="2:9">
       <c r="B99" s="3"/>
       <c r="C99" s="3" t="s">
         <v>12</v>
@@ -3623,7 +3636,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="100" ht="15" spans="2:9">
+    <row r="100" ht="17.55" spans="2:9">
       <c r="B100" s="3"/>
       <c r="C100" s="3" t="s">
         <v>13</v>
@@ -3647,7 +3660,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="101" ht="24.75" spans="2:9">
+    <row r="101" ht="28.75" spans="2:9">
       <c r="B101" s="3"/>
       <c r="C101" s="3" t="s">
         <v>15</v>
@@ -3671,7 +3684,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="102" ht="15" spans="2:9">
+    <row r="102" ht="17.55" spans="2:9">
       <c r="B102" s="3"/>
       <c r="C102" s="3" t="s">
         <v>17</v>
@@ -3695,7 +3708,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="103" ht="15" spans="2:9">
+    <row r="103" ht="17.55" spans="2:9">
       <c r="B103" s="3"/>
       <c r="C103" s="3" t="s">
         <v>18</v>
@@ -3719,7 +3732,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="104" ht="24.75" spans="2:9">
+    <row r="104" ht="28.75" spans="2:9">
       <c r="B104" s="3"/>
       <c r="C104" s="3" t="s">
         <v>28</v>
@@ -3743,7 +3756,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="105" ht="15" spans="2:9">
+    <row r="105" ht="17.55" spans="2:9">
       <c r="B105" s="3"/>
       <c r="C105" s="3" t="s">
         <v>32</v>
@@ -3767,7 +3780,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="106" ht="15" spans="2:9">
+    <row r="106" ht="17.55" spans="2:9">
       <c r="B106" s="3"/>
       <c r="C106" s="3" t="s">
         <v>33</v>
@@ -3791,7 +3804,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="107" ht="15" spans="2:9">
+    <row r="107" ht="17.55" spans="2:9">
       <c r="B107" s="3"/>
       <c r="C107" s="3" t="s">
         <v>34</v>
@@ -3815,7 +3828,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="108" ht="15" spans="2:9">
+    <row r="108" ht="17.55" spans="2:9">
       <c r="B108" s="3"/>
       <c r="C108" s="3" t="s">
         <v>20</v>
@@ -3839,7 +3852,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="109" ht="36.75" spans="2:9">
+    <row r="109" ht="56.75" spans="2:9">
       <c r="B109" s="3"/>
       <c r="C109" s="3" t="s">
         <v>75</v>
@@ -3863,7 +3876,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="110" ht="36.75" spans="2:9">
+    <row r="110" ht="42.75" spans="2:9">
       <c r="B110" s="3"/>
       <c r="C110" s="3" t="s">
         <v>76</v>
@@ -3887,7 +3900,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="111" ht="36.75" spans="2:9">
+    <row r="111" ht="42.75" spans="2:9">
       <c r="B111" s="3"/>
       <c r="C111" s="3" t="s">
         <v>77</v>
@@ -3911,7 +3924,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="112" ht="36.75" spans="2:9">
+    <row r="112" ht="42.75" spans="2:9">
       <c r="B112" s="3"/>
       <c r="C112" s="3" t="s">
         <v>78</v>
@@ -3935,7 +3948,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="113" ht="48.75" spans="2:9">
+    <row r="113" ht="56.75" spans="2:9">
       <c r="B113" s="3"/>
       <c r="C113" s="3" t="s">
         <v>79</v>
@@ -3959,7 +3972,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="114" ht="24.75" spans="2:9">
+    <row r="114" ht="28.75" spans="2:9">
       <c r="B114" s="3"/>
       <c r="C114" s="3" t="s">
         <v>39</v>
@@ -3983,7 +3996,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="115" ht="36.75" spans="2:9">
+    <row r="115" ht="42.75" spans="2:9">
       <c r="B115" s="3"/>
       <c r="C115" s="3" t="s">
         <v>80</v>
@@ -4007,7 +4020,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="116" ht="15" spans="2:9">
+    <row r="116" ht="17.55" spans="2:9">
       <c r="B116" s="3"/>
       <c r="C116" s="3" t="s">
         <v>42</v>
@@ -4031,7 +4044,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="117" ht="15" spans="2:9">
+    <row r="117" ht="17.55" spans="2:9">
       <c r="B117" s="3"/>
       <c r="C117" s="3" t="s">
         <v>44</v>
@@ -4055,7 +4068,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="118" ht="15" spans="2:9">
+    <row r="118" ht="17.55" spans="2:9">
       <c r="B118" s="3"/>
       <c r="C118" s="3" t="s">
         <v>19</v>
@@ -4079,7 +4092,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="119" ht="24.75" spans="2:9">
+    <row r="119" ht="28.75" spans="2:9">
       <c r="B119" s="3"/>
       <c r="C119" s="3" t="s">
         <v>68</v>
@@ -4103,7 +4116,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="120" ht="15" spans="2:9">
+    <row r="120" ht="28.75" spans="2:9">
       <c r="B120" s="3"/>
       <c r="C120" s="3" t="s">
         <v>23</v>
@@ -4127,7 +4140,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="121" ht="24.75" spans="2:9">
+    <row r="121" ht="28.75" spans="2:9">
       <c r="B121" s="3"/>
       <c r="C121" s="3" t="s">
         <v>26</v>
@@ -4151,7 +4164,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="122" ht="24.75" spans="2:9">
+    <row r="122" ht="28.75" spans="2:9">
       <c r="B122" s="3"/>
       <c r="C122" s="3" t="s">
         <v>46</v>
@@ -4185,7 +4198,7 @@
       <c r="H123" s="3"/>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" ht="15" spans="2:9">
+    <row r="124" ht="17.55" spans="2:9">
       <c r="B124" s="3" t="s">
         <v>81</v>
       </c>
@@ -4223,7 +4236,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" ht="15" spans="2:9">
+    <row r="126" ht="17.55" spans="2:9">
       <c r="B126" s="3" t="s">
         <v>82</v>
       </c>
@@ -4249,7 +4262,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="127" ht="24.75" spans="2:9">
+    <row r="127" ht="28.75" spans="2:9">
       <c r="B127" s="3"/>
       <c r="C127" s="3" t="s">
         <v>28</v>
@@ -4273,7 +4286,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="128" ht="24.75" spans="2:9">
+    <row r="128" ht="28.75" spans="2:9">
       <c r="B128" s="3"/>
       <c r="C128" s="3" t="s">
         <v>27</v>
@@ -4297,7 +4310,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="129" ht="15" spans="2:9">
+    <row r="129" ht="17.55" spans="2:9">
       <c r="B129" s="3"/>
       <c r="C129" s="3" t="s">
         <v>83</v>
@@ -4321,7 +4334,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="130" ht="15" spans="2:9">
+    <row r="130" ht="17.55" spans="2:9">
       <c r="B130" s="3"/>
       <c r="C130" s="3" t="s">
         <v>19</v>
@@ -4345,7 +4358,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="131" ht="15" spans="2:9">
+    <row r="131" ht="17.55" spans="2:9">
       <c r="B131" s="3"/>
       <c r="C131" s="3" t="s">
         <v>38</v>
@@ -4369,7 +4382,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="132" ht="24.75" spans="2:9">
+    <row r="132" ht="28.75" spans="2:9">
       <c r="B132" s="3"/>
       <c r="C132" s="3" t="s">
         <v>36</v>
@@ -4393,7 +4406,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="133" ht="15" spans="2:9">
+    <row r="133" ht="28.75" spans="2:9">
       <c r="B133" s="3"/>
       <c r="C133" s="3" t="s">
         <v>40</v>
@@ -4417,7 +4430,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="134" ht="24.75" spans="2:9">
+    <row r="134" ht="28.75" spans="2:9">
       <c r="B134" s="3"/>
       <c r="C134" s="3" t="s">
         <v>39</v>
@@ -4441,7 +4454,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="135" ht="24.75" spans="2:9">
+    <row r="135" ht="42.75" spans="2:9">
       <c r="B135" s="3"/>
       <c r="C135" s="3" t="s">
         <v>41</v>
@@ -4465,7 +4478,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="136" ht="15" spans="2:9">
+    <row r="136" ht="17.55" spans="2:9">
       <c r="B136" s="3"/>
       <c r="C136" s="3" t="s">
         <v>17</v>
@@ -4489,7 +4502,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="137" ht="15" spans="2:9">
+    <row r="137" ht="17.55" spans="2:9">
       <c r="B137" s="3"/>
       <c r="C137" s="3" t="s">
         <v>42</v>
@@ -4513,7 +4526,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="138" ht="24.75" spans="2:9">
+    <row r="138" ht="42.75" spans="2:9">
       <c r="B138" s="3"/>
       <c r="C138" s="3" t="s">
         <v>84</v>
@@ -4537,7 +4550,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="139" ht="15" spans="2:9">
+    <row r="139" ht="17.55" spans="2:9">
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
         <v>16</v>
@@ -4561,7 +4574,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="140" ht="15" spans="2:9">
+    <row r="140" ht="17.55" spans="2:9">
       <c r="B140" s="3"/>
       <c r="C140" s="3" t="s">
         <v>44</v>
@@ -4585,7 +4598,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="141" ht="36.75" spans="2:9">
+    <row r="141" ht="42.75" spans="2:9">
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
         <v>85</v>
@@ -4609,7 +4622,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="142" ht="15" spans="2:9">
+    <row r="142" ht="17.55" spans="2:9">
       <c r="B142" s="3"/>
       <c r="C142" s="3" t="s">
         <v>11</v>
@@ -4633,7 +4646,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="143" ht="15" spans="2:9">
+    <row r="143" ht="17.55" spans="2:9">
       <c r="B143" s="3"/>
       <c r="C143" s="3" t="s">
         <v>12</v>
@@ -4657,7 +4670,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="144" ht="15" spans="2:9">
+    <row r="144" ht="17.55" spans="2:9">
       <c r="B144" s="3"/>
       <c r="C144" s="3" t="s">
         <v>13</v>
@@ -4681,7 +4694,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="145" ht="15" spans="2:9">
+    <row r="145" ht="17.55" spans="2:9">
       <c r="B145" s="3"/>
       <c r="C145" s="3" t="s">
         <v>33</v>
@@ -4729,7 +4742,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="147" ht="15" spans="2:9">
+    <row r="147" ht="17.55" spans="2:9">
       <c r="B147" s="3" t="s">
         <v>86</v>
       </c>
@@ -4755,7 +4768,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="148" ht="15" spans="2:9">
+    <row r="148" ht="17.55" spans="2:9">
       <c r="B148" s="3"/>
       <c r="C148" s="3" t="s">
         <v>34</v>
@@ -4779,7 +4792,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="149" ht="15" spans="2:9">
+    <row r="149" ht="28.75" spans="2:9">
       <c r="B149" s="3"/>
       <c r="C149" s="3" t="s">
         <v>23</v>
@@ -4803,7 +4816,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="150" ht="24.75" spans="2:9">
+    <row r="150" ht="28.75" spans="2:9">
       <c r="B150" s="3"/>
       <c r="C150" s="3" t="s">
         <v>27</v>
@@ -4827,7 +4840,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="151" ht="15" spans="2:9">
+    <row r="151" ht="17.55" spans="2:9">
       <c r="B151" s="3"/>
       <c r="C151" s="3" t="s">
         <v>20</v>
@@ -4851,7 +4864,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="152" ht="15" spans="2:9">
+    <row r="152" ht="17.55" spans="2:9">
       <c r="B152" s="3"/>
       <c r="C152" s="3" t="s">
         <v>19</v>
@@ -4875,7 +4888,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="153" ht="15" spans="2:9">
+    <row r="153" ht="17.55" spans="2:9">
       <c r="B153" s="3"/>
       <c r="C153" s="3" t="s">
         <v>24</v>
@@ -4899,7 +4912,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="154" ht="24.75" spans="2:9">
+    <row r="154" ht="28.75" spans="2:9">
       <c r="B154" s="3"/>
       <c r="C154" s="3" t="s">
         <v>26</v>
@@ -4923,7 +4936,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="155" ht="15" spans="2:9">
+    <row r="155" ht="17.55" spans="2:9">
       <c r="B155" s="3"/>
       <c r="C155" s="3" t="s">
         <v>11</v>
@@ -4947,7 +4960,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="156" ht="15" spans="2:9">
+    <row r="156" ht="17.55" spans="2:9">
       <c r="B156" s="3"/>
       <c r="C156" s="3" t="s">
         <v>12</v>
@@ -4971,7 +4984,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="157" ht="15" spans="2:9">
+    <row r="157" ht="17.55" spans="2:9">
       <c r="B157" s="3"/>
       <c r="C157" s="3" t="s">
         <v>13</v>
@@ -4995,7 +5008,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="158" ht="15" spans="2:9">
+    <row r="158" ht="17.55" spans="2:9">
       <c r="B158" s="3"/>
       <c r="C158" s="3" t="s">
         <v>14</v>
@@ -5019,7 +5032,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="159" ht="24.75" spans="2:9">
+    <row r="159" ht="28.75" spans="2:9">
       <c r="B159" s="3"/>
       <c r="C159" s="3" t="s">
         <v>15</v>
@@ -5067,7 +5080,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="161" ht="15" spans="2:9">
+    <row r="161" ht="17.55" spans="2:9">
       <c r="B161" s="3" t="s">
         <v>87</v>
       </c>
@@ -5105,7 +5118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" ht="15" spans="2:9">
+    <row r="163" ht="17.55" spans="2:9">
       <c r="B163" s="3" t="s">
         <v>82</v>
       </c>
@@ -5131,7 +5144,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="164" ht="15" spans="2:9">
+    <row r="164" ht="17.55" spans="2:9">
       <c r="B164" s="3"/>
       <c r="C164" s="3" t="s">
         <v>38</v>
@@ -5155,7 +5168,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="165" ht="24.75" spans="2:9">
+    <row r="165" ht="28.75" spans="2:9">
       <c r="B165" s="3"/>
       <c r="C165" s="3" t="s">
         <v>36</v>
@@ -5179,7 +5192,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="166" ht="15" spans="2:9">
+    <row r="166" ht="28.75" spans="2:9">
       <c r="B166" s="3"/>
       <c r="C166" s="3" t="s">
         <v>40</v>
@@ -5203,7 +5216,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="167" ht="24.75" spans="2:9">
+    <row r="167" ht="28.75" spans="2:9">
       <c r="B167" s="3"/>
       <c r="C167" s="3" t="s">
         <v>39</v>
@@ -5227,7 +5240,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="168" ht="24.75" spans="2:9">
+    <row r="168" ht="28.75" spans="2:9">
       <c r="B168" s="3"/>
       <c r="C168" s="3" t="s">
         <v>47</v>
@@ -5251,7 +5264,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="169" ht="15" spans="2:9">
+    <row r="169" ht="17.55" spans="2:9">
       <c r="B169" s="3"/>
       <c r="C169" s="3" t="s">
         <v>44</v>
@@ -5275,7 +5288,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="170" ht="24.75" spans="2:9">
+    <row r="170" ht="28.75" spans="2:9">
       <c r="B170" s="3"/>
       <c r="C170" s="3" t="s">
         <v>28</v>
@@ -5299,7 +5312,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="171" ht="15" spans="2:9">
+    <row r="171" ht="17.55" spans="2:9">
       <c r="B171" s="3"/>
       <c r="C171" s="3" t="s">
         <v>19</v>
@@ -5323,7 +5336,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="172" ht="15" spans="2:9">
+    <row r="172" ht="17.55" spans="2:9">
       <c r="B172" s="3"/>
       <c r="C172" s="3" t="s">
         <v>22</v>
@@ -5347,7 +5360,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="173" ht="24.75" spans="2:9">
+    <row r="173" ht="28.75" spans="2:9">
       <c r="B173" s="3"/>
       <c r="C173" s="3" t="s">
         <v>26</v>
@@ -5371,7 +5384,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="174" ht="15" spans="2:9">
+    <row r="174" ht="17.55" spans="2:9">
       <c r="B174" s="3"/>
       <c r="C174" s="3" t="s">
         <v>17</v>
@@ -5419,7 +5432,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="176" ht="15" spans="2:9">
+    <row r="176" ht="28.75" spans="2:9">
       <c r="B176" s="3" t="s">
         <v>86</v>
       </c>
@@ -5445,7 +5458,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="177" ht="24.75" spans="2:9">
+    <row r="177" ht="28.75" spans="2:9">
       <c r="B177" s="3"/>
       <c r="C177" s="3" t="s">
         <v>27</v>
@@ -5469,7 +5482,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="178" ht="15" spans="2:9">
+    <row r="178" ht="17.55" spans="2:9">
       <c r="B178" s="3"/>
       <c r="C178" s="3" t="s">
         <v>25</v>
@@ -5493,7 +5506,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="179" ht="15" spans="2:9">
+    <row r="179" ht="17.55" spans="2:9">
       <c r="B179" s="3"/>
       <c r="C179" s="3" t="s">
         <v>20</v>
@@ -5517,7 +5530,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="180" ht="15" spans="2:9">
+    <row r="180" ht="17.55" spans="2:9">
       <c r="B180" s="3"/>
       <c r="C180" s="3" t="s">
         <v>19</v>
@@ -5541,7 +5554,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="181" ht="15" spans="2:9">
+    <row r="181" ht="17.55" spans="2:9">
       <c r="B181" s="3"/>
       <c r="C181" s="3" t="s">
         <v>22</v>
@@ -5565,7 +5578,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="182" ht="15" spans="2:9">
+    <row r="182" ht="17.55" spans="2:9">
       <c r="B182" s="3"/>
       <c r="C182" s="3" t="s">
         <v>24</v>
@@ -5589,7 +5602,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="183" ht="24.75" spans="2:9">
+    <row r="183" ht="28.75" spans="2:9">
       <c r="B183" s="3"/>
       <c r="C183" s="3" t="s">
         <v>26</v>
@@ -5613,7 +5626,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="184" ht="15" spans="2:9">
+    <row r="184" ht="17.55" spans="2:9">
       <c r="B184" s="3"/>
       <c r="C184" s="3" t="s">
         <v>31</v>
@@ -5637,7 +5650,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="185" ht="24.75" spans="2:9">
+    <row r="185" ht="28.75" spans="2:9">
       <c r="B185" s="3"/>
       <c r="C185" s="3" t="s">
         <v>30</v>
@@ -5671,7 +5684,7 @@
       <c r="H186" s="3"/>
       <c r="I186" s="3"/>
     </row>
-    <row r="187" ht="15" spans="2:9">
+    <row r="187" ht="17.55" spans="2:9">
       <c r="B187" s="3" t="s">
         <v>88</v>
       </c>
@@ -5709,7 +5722,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" ht="15" spans="2:9">
+    <row r="189" ht="17.55" spans="2:9">
       <c r="B189" s="3" t="s">
         <v>82</v>
       </c>
@@ -5735,7 +5748,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="190" ht="24.75" spans="2:9">
+    <row r="190" ht="28.75" spans="2:9">
       <c r="B190" s="3"/>
       <c r="C190" s="3" t="s">
         <v>36</v>
@@ -5759,7 +5772,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="191" ht="15" spans="2:9">
+    <row r="191" ht="17.55" spans="2:9">
       <c r="B191" s="3"/>
       <c r="C191" s="3" t="s">
         <v>37</v>
@@ -5783,7 +5796,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="192" ht="15" spans="2:9">
+    <row r="192" ht="17.55" spans="2:9">
       <c r="B192" s="3"/>
       <c r="C192" s="3" t="s">
         <v>38</v>
@@ -5807,7 +5820,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="193" ht="15" spans="2:9">
+    <row r="193" ht="28.75" spans="2:9">
       <c r="B193" s="3"/>
       <c r="C193" s="3" t="s">
         <v>40</v>
@@ -5831,7 +5844,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="194" ht="15" spans="2:9">
+    <row r="194" ht="17.55" spans="2:9">
       <c r="B194" s="3"/>
       <c r="C194" s="3" t="s">
         <v>16</v>
@@ -5855,7 +5868,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="195" ht="15" spans="2:9">
+    <row r="195" ht="17.55" spans="2:9">
       <c r="B195" s="3"/>
       <c r="C195" s="3" t="s">
         <v>13</v>
@@ -5879,7 +5892,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="196" ht="15" spans="2:9">
+    <row r="196" ht="17.55" spans="2:9">
       <c r="B196" s="3"/>
       <c r="C196" s="3" t="s">
         <v>12</v>
@@ -5903,7 +5916,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="197" ht="15" spans="2:9">
+    <row r="197" ht="17.55" spans="2:9">
       <c r="B197" s="3"/>
       <c r="C197" s="3" t="s">
         <v>11</v>
@@ -5927,7 +5940,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="198" ht="24.75" spans="2:9">
+    <row r="198" ht="28.75" spans="2:9">
       <c r="B198" s="3"/>
       <c r="C198" s="3" t="s">
         <v>46</v>
@@ -5951,7 +5964,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="199" ht="24.75" spans="2:9">
+    <row r="199" ht="42.75" spans="2:9">
       <c r="B199" s="3"/>
       <c r="C199" s="3" t="s">
         <v>41</v>
@@ -5975,7 +5988,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="200" ht="15" spans="2:9">
+    <row r="200" ht="17.55" spans="2:9">
       <c r="B200" s="3"/>
       <c r="C200" s="3" t="s">
         <v>17</v>
@@ -5999,7 +6012,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="201" ht="15" spans="2:9">
+    <row r="201" ht="17.55" spans="2:9">
       <c r="B201" s="3"/>
       <c r="C201" s="3" t="s">
         <v>20</v>
@@ -6023,7 +6036,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="202" ht="15" spans="2:9">
+    <row r="202" ht="17.55" spans="2:9">
       <c r="B202" s="3"/>
       <c r="C202" s="3" t="s">
         <v>22</v>
@@ -6047,7 +6060,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="203" ht="24.75" spans="2:9">
+    <row r="203" ht="28.75" spans="2:9">
       <c r="B203" s="3"/>
       <c r="C203" s="3" t="s">
         <v>47</v>
@@ -6095,7 +6108,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="205" ht="15" spans="2:9">
+    <row r="205" ht="17.55" spans="2:9">
       <c r="B205" s="3" t="s">
         <v>86</v>
       </c>
@@ -6121,7 +6134,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="206" ht="24.75" spans="2:9">
+    <row r="206" ht="28.75" spans="2:9">
       <c r="B206" s="3"/>
       <c r="C206" s="3" t="s">
         <v>15</v>
@@ -6145,7 +6158,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="207" ht="15" spans="2:9">
+    <row r="207" ht="17.55" spans="2:9">
       <c r="B207" s="3"/>
       <c r="C207" s="3" t="s">
         <v>13</v>
@@ -6169,7 +6182,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="208" ht="15" spans="2:9">
+    <row r="208" ht="17.55" spans="2:9">
       <c r="B208" s="3"/>
       <c r="C208" s="3" t="s">
         <v>12</v>
@@ -6193,7 +6206,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="209" ht="15" spans="2:9">
+    <row r="209" ht="17.55" spans="2:9">
       <c r="B209" s="3"/>
       <c r="C209" s="3" t="s">
         <v>11</v>
@@ -6217,7 +6230,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="210" ht="24.75" spans="2:9">
+    <row r="210" ht="28.75" spans="2:9">
       <c r="B210" s="3"/>
       <c r="C210" s="3" t="s">
         <v>30</v>
@@ -6241,7 +6254,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="211" ht="15" spans="2:9">
+    <row r="211" ht="17.55" spans="2:9">
       <c r="B211" s="3"/>
       <c r="C211" s="3" t="s">
         <v>48</v>
@@ -6265,7 +6278,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="212" ht="15" spans="2:9">
+    <row r="212" ht="17.55" spans="2:9">
       <c r="B212" s="3"/>
       <c r="C212" s="3" t="s">
         <v>22</v>
@@ -6289,7 +6302,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="213" ht="15" spans="2:9">
+    <row r="213" ht="28.75" spans="2:9">
       <c r="B213" s="3"/>
       <c r="C213" s="3" t="s">
         <v>23</v>
@@ -6313,7 +6326,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="214" ht="15" spans="2:9">
+    <row r="214" ht="17.55" spans="2:9">
       <c r="B214" s="3"/>
       <c r="C214" s="3" t="s">
         <v>25</v>
@@ -6361,7 +6374,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="216" ht="15" spans="2:9">
+    <row r="216" ht="17.55" spans="2:9">
       <c r="B216" s="3" t="s">
         <v>89</v>
       </c>
@@ -6411,7 +6424,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="218" ht="15" spans="2:9">
+    <row r="218" ht="17.55" spans="2:9">
       <c r="B218" s="3" t="s">
         <v>90</v>
       </c>
@@ -6461,7 +6474,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="220" ht="15" spans="2:9">
+    <row r="220" ht="17.55" spans="2:9">
       <c r="B220" s="3" t="s">
         <v>92</v>
       </c>
@@ -6499,7 +6512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" ht="15" spans="2:9">
+    <row r="222" ht="17.55" spans="2:9">
       <c r="B222" s="3" t="s">
         <v>82</v>
       </c>
@@ -6525,7 +6538,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="223" ht="24.75" spans="2:9">
+    <row r="223" ht="28.75" spans="2:9">
       <c r="B223" s="3"/>
       <c r="C223" s="3" t="s">
         <v>26</v>
@@ -6549,7 +6562,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="224" ht="24.75" spans="2:9">
+    <row r="224" ht="28.75" spans="2:9">
       <c r="B224" s="3"/>
       <c r="C224" s="3" t="s">
         <v>27</v>
@@ -6573,7 +6586,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="225" ht="24.75" spans="2:9">
+    <row r="225" ht="28.75" spans="2:9">
       <c r="B225" s="3"/>
       <c r="C225" s="3" t="s">
         <v>28</v>
@@ -6597,7 +6610,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="226" ht="48.75" spans="2:9">
+    <row r="226" ht="70.75" spans="2:9">
       <c r="B226" s="3"/>
       <c r="C226" s="3" t="s">
         <v>29</v>
@@ -6621,7 +6634,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="227" ht="15" spans="2:9">
+    <row r="227" ht="17.55" spans="2:9">
       <c r="B227" s="3"/>
       <c r="C227" s="3" t="s">
         <v>32</v>
@@ -6645,7 +6658,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="228" ht="15" spans="2:9">
+    <row r="228" ht="17.55" spans="2:9">
       <c r="B228" s="3"/>
       <c r="C228" s="3" t="s">
         <v>37</v>
@@ -6669,7 +6682,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="229" ht="24.75" spans="2:9">
+    <row r="229" ht="28.75" spans="2:9">
       <c r="B229" s="3"/>
       <c r="C229" s="3" t="s">
         <v>39</v>
@@ -6693,7 +6706,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="230" ht="24.75" spans="2:9">
+    <row r="230" ht="42.75" spans="2:9">
       <c r="B230" s="3"/>
       <c r="C230" s="3" t="s">
         <v>41</v>
@@ -6717,7 +6730,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="231" ht="15" spans="2:9">
+    <row r="231" ht="17.55" spans="2:9">
       <c r="B231" s="3"/>
       <c r="C231" s="3" t="s">
         <v>42</v>
@@ -6765,7 +6778,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="233" ht="15" spans="2:9">
+    <row r="233" ht="28.75" spans="2:9">
       <c r="B233" s="3" t="s">
         <v>86</v>
       </c>
@@ -6791,7 +6804,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="234" ht="15" spans="2:9">
+    <row r="234" ht="17.55" spans="2:9">
       <c r="B234" s="3"/>
       <c r="C234" s="3" t="s">
         <v>24</v>
@@ -6815,7 +6828,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="235" ht="24.75" spans="2:9">
+    <row r="235" ht="28.75" spans="2:9">
       <c r="B235" s="3"/>
       <c r="C235" s="3" t="s">
         <v>26</v>
@@ -6839,7 +6852,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="236" ht="24.75" spans="2:9">
+    <row r="236" ht="28.75" spans="2:9">
       <c r="B236" s="3"/>
       <c r="C236" s="3" t="s">
         <v>27</v>
@@ -6863,7 +6876,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="237" ht="48.75" spans="2:9">
+    <row r="237" ht="70.75" spans="2:9">
       <c r="B237" s="3"/>
       <c r="C237" s="3" t="s">
         <v>29</v>
@@ -6887,7 +6900,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="238" ht="15" spans="2:9">
+    <row r="238" ht="17.55" spans="2:9">
       <c r="B238" s="3"/>
       <c r="C238" s="3" t="s">
         <v>31</v>
@@ -6911,7 +6924,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="239" ht="15" spans="2:9">
+    <row r="239" ht="17.55" spans="2:9">
       <c r="B239" s="3"/>
       <c r="C239" s="3" t="s">
         <v>34</v>
@@ -6935,7 +6948,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="240" ht="15" spans="2:9">
+    <row r="240" ht="17.55" spans="2:9">
       <c r="B240" s="3"/>
       <c r="C240" s="3" t="s">
         <v>20</v>
@@ -6983,7 +6996,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="242" ht="15" spans="2:9">
+    <row r="242" ht="17.55" spans="2:9">
       <c r="B242" s="3" t="s">
         <v>93</v>
       </c>
@@ -6995,7 +7008,7 @@
       <c r="H242" s="3"/>
       <c r="I242" s="3"/>
     </row>
-    <row r="243" ht="14.25" spans="2:9">
+    <row r="243" ht="17.55" spans="2:9">
       <c r="B243" s="3" t="s">
         <v>2</v>
       </c>
@@ -7047,7 +7060,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="245" ht="24.75" spans="2:9">
+    <row r="245" ht="28.75" spans="2:9">
       <c r="B245" s="3" t="s">
         <v>86</v>
       </c>
@@ -7097,7 +7110,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="247" ht="15" spans="2:9">
+    <row r="247" ht="17.55" spans="2:9">
       <c r="B247" s="3" t="s">
         <v>94</v>
       </c>
@@ -7135,7 +7148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" ht="24.75" spans="2:9">
+    <row r="249" ht="28.75" spans="2:9">
       <c r="B249" s="3" t="s">
         <v>82</v>
       </c>
@@ -7161,7 +7174,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="250" ht="15" spans="2:9">
+    <row r="250" ht="28.75" spans="2:9">
       <c r="B250" s="3"/>
       <c r="C250" s="3" t="s">
         <v>40</v>
@@ -7185,7 +7198,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="251" ht="15" spans="2:9">
+    <row r="251" ht="17.55" spans="2:9">
       <c r="B251" s="3"/>
       <c r="C251" s="3" t="s">
         <v>44</v>
@@ -7209,7 +7222,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="252" ht="24.75" spans="2:9">
+    <row r="252" ht="28.75" spans="2:9">
       <c r="B252" s="3"/>
       <c r="C252" s="3" t="s">
         <v>47</v>
@@ -7257,7 +7270,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="254" ht="15" spans="2:9">
+    <row r="254" ht="17.55" spans="2:9">
       <c r="B254" s="3" t="s">
         <v>95</v>
       </c>
@@ -7295,7 +7308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="256" ht="15" spans="2:9">
+    <row r="256" ht="17.55" spans="2:9">
       <c r="B256" s="3" t="s">
         <v>82</v>
       </c>
@@ -7321,7 +7334,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="257" ht="15" spans="2:9">
+    <row r="257" ht="28.75" spans="2:9">
       <c r="B257" s="3"/>
       <c r="C257" s="3" t="s">
         <v>23</v>
@@ -7345,7 +7358,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="258" ht="24.75" spans="2:9">
+    <row r="258" ht="28.75" spans="2:9">
       <c r="B258" s="3"/>
       <c r="C258" s="3" t="s">
         <v>26</v>
@@ -7369,7 +7382,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="259" ht="24.75" spans="2:9">
+    <row r="259" ht="28.75" spans="2:9">
       <c r="B259" s="3"/>
       <c r="C259" s="3" t="s">
         <v>28</v>
@@ -7393,7 +7406,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="260" ht="15" spans="2:9">
+    <row r="260" ht="17.55" spans="2:9">
       <c r="B260" s="3"/>
       <c r="C260" s="3" t="s">
         <v>37</v>
@@ -7417,7 +7430,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="261" ht="24.75" spans="2:9">
+    <row r="261" ht="28.75" spans="2:9">
       <c r="B261" s="3"/>
       <c r="C261" s="3" t="s">
         <v>39</v>
@@ -7441,7 +7454,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="262" ht="15" spans="2:9">
+    <row r="262" ht="17.55" spans="2:9">
       <c r="B262" s="3"/>
       <c r="C262" s="3" t="s">
         <v>45</v>
@@ -7489,7 +7502,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="264" ht="15" spans="2:9">
+    <row r="264" ht="17.55" spans="2:9">
       <c r="B264" s="3" t="s">
         <v>86</v>
       </c>
@@ -7515,7 +7528,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="265" ht="15" spans="2:9">
+    <row r="265" ht="17.55" spans="2:9">
       <c r="B265" s="3"/>
       <c r="C265" s="3" t="s">
         <v>22</v>
@@ -7539,7 +7552,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="266" ht="15" spans="2:9">
+    <row r="266" ht="28.75" spans="2:9">
       <c r="B266" s="3"/>
       <c r="C266" s="3" t="s">
         <v>23</v>
@@ -7563,7 +7576,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="267" ht="15" spans="2:9">
+    <row r="267" ht="17.55" spans="2:9">
       <c r="B267" s="3"/>
       <c r="C267" s="3" t="s">
         <v>24</v>
@@ -7587,7 +7600,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="268" ht="15" spans="2:9">
+    <row r="268" ht="17.55" spans="2:9">
       <c r="B268" s="3"/>
       <c r="C268" s="3" t="s">
         <v>25</v>
@@ -7611,7 +7624,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="269" ht="24.75" spans="2:9">
+    <row r="269" ht="28.75" spans="2:9">
       <c r="B269" s="3"/>
       <c r="C269" s="3" t="s">
         <v>26</v>
@@ -7635,7 +7648,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="270" ht="24.75" spans="2:9">
+    <row r="270" ht="28.75" spans="2:9">
       <c r="B270" s="3"/>
       <c r="C270" s="3" t="s">
         <v>27</v>
@@ -7659,7 +7672,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="271" ht="48.75" spans="2:9">
+    <row r="271" ht="70.75" spans="2:9">
       <c r="B271" s="3"/>
       <c r="C271" s="3" t="s">
         <v>29</v>
@@ -7693,7 +7706,7 @@
       <c r="H272" s="3"/>
       <c r="I272" s="3"/>
     </row>
-    <row r="273" ht="15" spans="2:9">
+    <row r="273" ht="17.55" spans="2:9">
       <c r="B273" s="3" t="s">
         <v>96</v>
       </c>
@@ -7731,7 +7744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="275" ht="15" spans="2:9">
+    <row r="275" ht="17.55" spans="2:9">
       <c r="B275" s="3" t="s">
         <v>82</v>
       </c>
@@ -7757,7 +7770,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="276" ht="15" spans="2:9">
+    <row r="276" ht="17.55" spans="2:9">
       <c r="B276" s="3"/>
       <c r="C276" s="3" t="s">
         <v>20</v>
@@ -7781,7 +7794,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="277" ht="15" spans="2:9">
+    <row r="277" ht="17.55" spans="2:9">
       <c r="B277" s="3"/>
       <c r="C277" s="3" t="s">
         <v>38</v>
@@ -7805,7 +7818,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="278" ht="24.75" spans="2:9">
+    <row r="278" ht="28.75" spans="2:9">
       <c r="B278" s="3"/>
       <c r="C278" s="3" t="s">
         <v>36</v>
@@ -7829,7 +7842,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="279" ht="15" spans="2:9">
+    <row r="279" ht="28.75" spans="2:9">
       <c r="B279" s="3"/>
       <c r="C279" s="3" t="s">
         <v>40</v>
@@ -7877,7 +7890,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="281" ht="24.75" spans="2:9">
+    <row r="281" ht="28.75" spans="2:9">
       <c r="B281" s="3" t="s">
         <v>86</v>
       </c>
@@ -7903,7 +7916,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="282" ht="15" spans="2:9">
+    <row r="282" ht="28.75" spans="2:9">
       <c r="B282" s="3"/>
       <c r="C282" s="3" t="s">
         <v>23</v>
@@ -7927,7 +7940,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="283" ht="24.75" spans="2:9">
+    <row r="283" ht="28.75" spans="2:9">
       <c r="B283" s="3"/>
       <c r="C283" s="3" t="s">
         <v>27</v>
@@ -7951,7 +7964,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="284" ht="15" spans="2:9">
+    <row r="284" ht="17.55" spans="2:9">
       <c r="B284" s="3"/>
       <c r="C284" s="3" t="s">
         <v>25</v>
@@ -7975,7 +7988,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="285" ht="15" spans="2:9">
+    <row r="285" ht="17.55" spans="2:9">
       <c r="B285" s="3"/>
       <c r="C285" s="3" t="s">
         <v>20</v>
@@ -7999,7 +8012,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="286" ht="15" spans="2:9">
+    <row r="286" ht="17.55" spans="2:9">
       <c r="B286" s="3"/>
       <c r="C286" s="3" t="s">
         <v>22</v>
@@ -8023,7 +8036,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="287" ht="15" spans="2:9">
+    <row r="287" ht="17.55" spans="2:9">
       <c r="B287" s="3"/>
       <c r="C287" s="3" t="s">
         <v>24</v>
@@ -8047,7 +8060,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="288" ht="24.75" spans="2:9">
+    <row r="288" ht="28.75" spans="2:9">
       <c r="B288" s="3"/>
       <c r="C288" s="3" t="s">
         <v>26</v>
@@ -8081,7 +8094,7 @@
       <c r="H289" s="3"/>
       <c r="I289" s="3"/>
     </row>
-    <row r="290" ht="15" spans="2:9">
+    <row r="290" ht="17.55" spans="2:9">
       <c r="B290" s="3" t="s">
         <v>97</v>
       </c>
@@ -8119,7 +8132,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" ht="15" spans="2:9">
+    <row r="292" ht="17.55" spans="2:9">
       <c r="B292" s="3" t="s">
         <v>82</v>
       </c>
@@ -8145,7 +8158,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="293" ht="15" spans="2:9">
+    <row r="293" ht="17.55" spans="2:9">
       <c r="B293" s="3"/>
       <c r="C293" s="3" t="s">
         <v>12</v>
@@ -8169,7 +8182,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="294" ht="15" spans="2:9">
+    <row r="294" ht="17.55" spans="2:9">
       <c r="B294" s="3"/>
       <c r="C294" s="3" t="s">
         <v>13</v>
@@ -8193,7 +8206,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="295" ht="15" spans="2:9">
+    <row r="295" ht="17.55" spans="2:9">
       <c r="B295" s="3"/>
       <c r="C295" s="3" t="s">
         <v>14</v>
@@ -8217,7 +8230,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="296" ht="15" spans="2:9">
+    <row r="296" ht="17.55" spans="2:9">
       <c r="B296" s="3"/>
       <c r="C296" s="3" t="s">
         <v>17</v>
@@ -8241,7 +8254,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="297" ht="15" spans="2:9">
+    <row r="297" ht="17.55" spans="2:9">
       <c r="B297" s="3"/>
       <c r="C297" s="3" t="s">
         <v>33</v>
@@ -8265,7 +8278,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="298" ht="24.75" spans="2:9">
+    <row r="298" ht="28.75" spans="2:9">
       <c r="B298" s="3"/>
       <c r="C298" s="3" t="s">
         <v>36</v>
@@ -8289,7 +8302,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="299" ht="15" spans="2:9">
+    <row r="299" ht="17.55" spans="2:9">
       <c r="B299" s="3"/>
       <c r="C299" s="3" t="s">
         <v>37</v>
@@ -8313,7 +8326,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="300" ht="15" spans="2:9">
+    <row r="300" ht="28.75" spans="2:9">
       <c r="B300" s="3"/>
       <c r="C300" s="3" t="s">
         <v>40</v>
@@ -8337,7 +8350,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="301" ht="15" spans="2:9">
+    <row r="301" ht="17.55" spans="2:9">
       <c r="B301" s="3"/>
       <c r="C301" s="3" t="s">
         <v>42</v>
@@ -8361,7 +8374,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="302" ht="15" spans="2:9">
+    <row r="302" ht="17.55" spans="2:9">
       <c r="B302" s="3"/>
       <c r="C302" s="3" t="s">
         <v>45</v>
@@ -8409,7 +8422,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="304" ht="15" spans="2:9">
+    <row r="304" ht="17.55" spans="2:9">
       <c r="B304" s="3" t="s">
         <v>86</v>
       </c>
@@ -8435,7 +8448,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="305" ht="15" spans="2:9">
+    <row r="305" ht="17.55" spans="2:9">
       <c r="B305" s="3"/>
       <c r="C305" s="3" t="s">
         <v>12</v>
@@ -8459,7 +8472,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="306" ht="15" spans="2:9">
+    <row r="306" ht="17.55" spans="2:9">
       <c r="B306" s="3"/>
       <c r="C306" s="3" t="s">
         <v>13</v>
@@ -8483,7 +8496,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="307" ht="15" spans="2:9">
+    <row r="307" ht="17.55" spans="2:9">
       <c r="B307" s="3"/>
       <c r="C307" s="3" t="s">
         <v>14</v>
@@ -8507,7 +8520,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="308" ht="24.75" spans="2:9">
+    <row r="308" ht="28.75" spans="2:9">
       <c r="B308" s="3"/>
       <c r="C308" s="3" t="s">
         <v>30</v>
@@ -8555,7 +8568,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="310" ht="15" spans="2:9">
+    <row r="310" ht="17.55" spans="2:9">
       <c r="B310" s="3" t="s">
         <v>99</v>
       </c>
@@ -8593,7 +8606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312" ht="15" spans="2:9">
+    <row r="312" ht="17.55" spans="2:9">
       <c r="B312" s="3" t="s">
         <v>74</v>
       </c>
@@ -8619,7 +8632,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="313" ht="15" spans="2:9">
+    <row r="313" ht="17.55" spans="2:9">
       <c r="B313" s="3"/>
       <c r="C313" s="3" t="s">
         <v>44</v>
@@ -8643,7 +8656,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="314" ht="15" spans="2:9">
+    <row r="314" ht="17.55" spans="2:9">
       <c r="B314" s="3"/>
       <c r="C314" s="3" t="s">
         <v>49</v>
@@ -8667,7 +8680,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="315" ht="15" spans="2:9">
+    <row r="315" ht="17.55" spans="2:9">
       <c r="B315" s="3"/>
       <c r="C315" s="3" t="s">
         <v>32</v>
@@ -8691,7 +8704,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="316" ht="24.75" spans="2:9">
+    <row r="316" ht="28.75" spans="2:9">
       <c r="B316" s="3"/>
       <c r="C316" s="3" t="s">
         <v>28</v>
@@ -8715,7 +8728,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="317" ht="48.75" spans="2:9">
+    <row r="317" ht="70.75" spans="2:9">
       <c r="B317" s="3"/>
       <c r="C317" s="3" t="s">
         <v>29</v>
@@ -8739,7 +8752,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="318" ht="15" spans="2:9">
+    <row r="318" ht="17.55" spans="2:9">
       <c r="B318" s="3"/>
       <c r="C318" s="3" t="s">
         <v>19</v>
@@ -8787,7 +8800,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="320" ht="48.75" spans="2:9">
+    <row r="320" ht="70.75" spans="2:9">
       <c r="B320" s="3" t="s">
         <v>72</v>
       </c>
@@ -8813,7 +8826,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="321" ht="24.75" spans="2:9">
+    <row r="321" ht="28.75" spans="2:9">
       <c r="B321" s="3"/>
       <c r="C321" s="3" t="s">
         <v>27</v>
@@ -8837,7 +8850,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="322" ht="15" spans="2:9">
+    <row r="322" ht="17.55" spans="2:9">
       <c r="B322" s="3"/>
       <c r="C322" s="3" t="s">
         <v>19</v>
@@ -8861,7 +8874,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="323" ht="15" spans="2:9">
+    <row r="323" ht="17.55" spans="2:9">
       <c r="B323" s="3"/>
       <c r="C323" s="3" t="s">
         <v>22</v>
@@ -8885,7 +8898,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="324" ht="15" spans="2:9">
+    <row r="324" ht="17.55" spans="2:9">
       <c r="B324" s="3"/>
       <c r="C324" s="3" t="s">
         <v>33</v>
@@ -8919,7 +8932,7 @@
       <c r="H325" s="3"/>
       <c r="I325" s="3"/>
     </row>
-    <row r="326" ht="15" spans="2:9">
+    <row r="326" ht="17.55" spans="2:9">
       <c r="B326" s="3" t="s">
         <v>100</v>
       </c>
@@ -8957,7 +8970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="328" ht="15" spans="2:9">
+    <row r="328" ht="17.55" spans="2:9">
       <c r="B328" s="3" t="s">
         <v>82</v>
       </c>
@@ -8983,7 +8996,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="329" ht="24.75" spans="2:9">
+    <row r="329" ht="28.75" spans="2:9">
       <c r="B329" s="3"/>
       <c r="C329" s="3" t="s">
         <v>36</v>
@@ -9007,7 +9020,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="330" ht="15" spans="2:9">
+    <row r="330" ht="17.55" spans="2:9">
       <c r="B330" s="3"/>
       <c r="C330" s="3" t="s">
         <v>38</v>
@@ -9031,7 +9044,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="331" ht="15" spans="2:9">
+    <row r="331" ht="28.75" spans="2:9">
       <c r="B331" s="3"/>
       <c r="C331" s="3" t="s">
         <v>40</v>
@@ -9055,7 +9068,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="332" ht="24.75" spans="2:9">
+    <row r="332" ht="42.75" spans="2:9">
       <c r="B332" s="3"/>
       <c r="C332" s="3" t="s">
         <v>41</v>
@@ -9079,7 +9092,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="333" ht="24.75" spans="2:9">
+    <row r="333" ht="28.75" spans="2:9">
       <c r="B333" s="3"/>
       <c r="C333" s="3" t="s">
         <v>46</v>
@@ -9103,7 +9116,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="334" ht="24.75" spans="2:9">
+    <row r="334" ht="28.75" spans="2:9">
       <c r="B334" s="3"/>
       <c r="C334" s="3" t="s">
         <v>47</v>
@@ -9151,7 +9164,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="336" ht="15" spans="2:9">
+    <row r="336" ht="17.55" spans="2:9">
       <c r="B336" s="3" t="s">
         <v>86</v>
       </c>
@@ -9177,7 +9190,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="337" ht="15" spans="2:9">
+    <row r="337" ht="17.55" spans="2:9">
       <c r="B337" s="3"/>
       <c r="C337" s="3" t="s">
         <v>25</v>
@@ -9201,7 +9214,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="338" ht="15" spans="2:9">
+    <row r="338" ht="17.55" spans="2:9">
       <c r="B338" s="3"/>
       <c r="C338" s="3" t="s">
         <v>33</v>
@@ -9249,7 +9262,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="340" ht="15" spans="2:9">
+    <row r="340" ht="17.55" spans="2:9">
       <c r="B340" s="3" t="s">
         <v>90</v>
       </c>
@@ -9275,7 +9288,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="341" ht="24.75" spans="2:9">
+    <row r="341" ht="28.75" spans="2:9">
       <c r="B341" s="3"/>
       <c r="C341" s="3" t="s">
         <v>53</v>
@@ -9299,7 +9312,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="342" ht="15" spans="2:9">
+    <row r="342" ht="17.55" spans="2:9">
       <c r="B342" s="3"/>
       <c r="C342" s="3" t="s">
         <v>54</v>
@@ -9347,7 +9360,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="344" ht="15" spans="2:9">
+    <row r="344" ht="17.55" spans="2:9">
       <c r="B344" s="3" t="s">
         <v>89</v>
       </c>
@@ -9373,7 +9386,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="345" ht="24.75" spans="2:9">
+    <row r="345" ht="28.75" spans="2:9">
       <c r="B345" s="3"/>
       <c r="C345" s="3" t="s">
         <v>53</v>
@@ -9397,7 +9410,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="346" ht="15" spans="2:9">
+    <row r="346" ht="17.55" spans="2:9">
       <c r="B346" s="3"/>
       <c r="C346" s="3" t="s">
         <v>54</v>
@@ -9445,7 +9458,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="348" ht="15" spans="2:9">
+    <row r="348" ht="17.55" spans="2:9">
       <c r="B348" s="3" t="s">
         <v>101</v>
       </c>
@@ -9483,7 +9496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="350" ht="24.75" spans="2:9">
+    <row r="350" ht="28.75" spans="2:9">
       <c r="B350" s="3" t="s">
         <v>86</v>
       </c>
@@ -9533,7 +9546,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="352" ht="15" spans="2:9">
+    <row r="352" ht="17.55" spans="2:9">
       <c r="B352" s="3" t="s">
         <v>102</v>
       </c>
@@ -9571,7 +9584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="354" ht="15" spans="2:9">
+    <row r="354" ht="17.55" spans="2:9">
       <c r="B354" s="3" t="s">
         <v>74</v>
       </c>
@@ -9597,7 +9610,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="355" ht="24.75" spans="2:9">
+    <row r="355" ht="28.75" spans="2:9">
       <c r="B355" s="3"/>
       <c r="C355" s="4" t="s">
         <v>28</v>
@@ -9621,7 +9634,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="356" ht="24.75" spans="2:9">
+    <row r="356" ht="28.75" spans="2:9">
       <c r="B356" s="3"/>
       <c r="C356" s="4" t="s">
         <v>43</v>
@@ -9645,7 +9658,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="357" ht="24.75" spans="2:9">
+    <row r="357" ht="28.75" spans="2:9">
       <c r="B357" s="4" t="s">
         <v>72</v>
       </c>
